--- a/MH/MH_Robotics_Financial_Model.xlsx
+++ b/MH/MH_Robotics_Financial_Model.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="951">
   <si>
     <t xml:space="preserve">MH Robotics — Seed + TIPS IR Financial Model (Draft v5, 2026-10)</t>
   </si>
@@ -3716,7 +3716,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">받은 평면 </t>
+      <t xml:space="preserve">가설</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확보 평면 </t>
     </r>
     <r>
       <rPr>
@@ -3735,26 +3754,145 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">종 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종만 기본 배치 수용 </t>
+      <t xml:space="preserve">종 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Remodeling </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기본 배치 수용 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미수용 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미검토 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로는 판단 불가 → 평면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상담 주방 실측으로 검증</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">a_retro_conv</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Retrofit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 전환율 </t>
     </r>
     <r>
       <rPr>
@@ -3773,7 +3911,225 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">표본 작음</t>
+      <t xml:space="preserve">호환 세대 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제품 성숙 후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가설</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. Phase 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시작 전 검증</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">a_new_supply</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간 신규 아파트 입주 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">평균</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">평균 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만</t>
     </r>
     <r>
       <rPr>
@@ -3792,252 +4148,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">평면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개로 검증</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">a_retro_conv</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Retrofit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 전환율 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">호환 세대 중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제품 성숙 후</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가설</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. Phase 2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시작 전 검증</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">a_new_supply</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 신규 아파트 입주 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">평균</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">DERIVED</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실적 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">23.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예정 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 → </t>
+      <t xml:space="preserve">보수적으로 </t>
     </r>
     <r>
       <rPr>
@@ -10505,6 +10616,9 @@
       </rPr>
       <t xml:space="preserve">10%, Y1~Y2)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED</t>
   </si>
   <si>
     <r>
@@ -15735,6 +15849,213 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단순 회수기간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개월</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매입가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 순유입</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Partner </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Payback (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개월</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회수기간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구치이면 매입가율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기간 협의 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
@@ -19082,19 +19403,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20% ↔ 60%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Failure Rate 0.3 ↔ 1.2</t>
+      <t xml:space="preserve">60% ↔ 20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Failure Rate 1.2 ↔ 0.3</t>
     </r>
     <r>
       <rPr>
@@ -33048,12 +33369,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33070,12 +33391,12 @@
         <v>5</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">Inputs!$E$5</f>
@@ -33088,12 +33409,12 @@
         <v>55</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B5" s="13" t="n">
         <f aca="false">Inputs!$E$6</f>
@@ -33109,7 +33430,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">B4*B5</f>
@@ -33119,15 +33440,15 @@
         <v>54</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">Inputs!$E$10/Inputs!$E$15</f>
@@ -33137,13 +33458,13 @@
         <v>94</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">Inputs!$E$11*Inputs!$E$16*Inputs!$E$17+Inputs!$E$18</f>
@@ -33153,13 +33474,13 @@
         <v>94</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">Inputs!$E$19</f>
@@ -33172,12 +33493,12 @@
         <v>84</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">Inputs!$E$20</f>
@@ -33193,7 +33514,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B11" s="27" t="n">
         <f aca="false">B9*B10</f>
@@ -33203,13 +33524,13 @@
         <v>94</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">Inputs!$E$21</f>
@@ -33225,7 +33546,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">B11*B12</f>
@@ -33235,49 +33556,49 @@
         <v>94</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">Inputs!$E$34+Inputs_Yearly!$I$45*(Inputs!$E$37+Inputs!$E$38)</f>
         <v>1784.5</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B15" s="27" t="n">
         <f aca="false">B13*B14/10</f>
         <v>3212.1</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">Inputs!$E$22</f>
@@ -33306,12 +33627,12 @@
         <v>84</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B18" s="13" t="n">
         <f aca="false">Inputs!$E$24</f>
@@ -33324,30 +33645,30 @@
         <v>84</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B19" s="27" t="n">
         <f aca="false">B6*B16*B17*B18</f>
         <v>318.698352</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">Inputs!$E$25</f>
@@ -33363,7 +33684,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B21" s="27" t="n">
         <f aca="false">B19*B20</f>
@@ -33373,47 +33694,47 @@
         <v>94</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B22" s="27" t="n">
         <f aca="false">Inputs!$E$36+Inputs!$E$37+Inputs!$E$39</f>
         <v>1760</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B23" s="27" t="n">
         <f aca="false">B21*B22/10</f>
         <v>280.45454976</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B24" s="11" t="n">
         <f aca="false">Inputs!$E$26</f>
@@ -33423,15 +33744,15 @@
         <v>94</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B25" s="13" t="n">
         <f aca="false">Inputs!$E$27</f>
@@ -33447,7 +33768,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">B24*B25</f>
@@ -33457,13 +33778,13 @@
         <v>94</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B27" s="13" t="n">
         <f aca="false">Inputs!$E$81</f>
@@ -33479,7 +33800,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">B26*B27</f>
@@ -33489,79 +33810,79 @@
         <v>94</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B29" s="27" t="n">
         <f aca="false">Inputs!$E$35+Inputs!$E$82*(Inputs!$E$37+Inputs!$E$38)</f>
         <v>612.5</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B30" s="27" t="n">
         <f aca="false">B28*B29/10</f>
         <v>183.75</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Inputs!$E$51*Inputs!$E$42+Inputs!$E$50*(Inputs!$E$44*Inputs!$E$45+Inputs!$E$46*Inputs!$E$47+Inputs!$E$48*Inputs!$E$49)</f>
         <v>58.8</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">B31*1000/10000</f>
         <v>5.88</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">FM_Base!$G$28</f>
@@ -33571,40 +33892,40 @@
         <v>41</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">FM_Base!$G$76/10000</f>
         <v>3.478281</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Inputs!$E$34+Inputs!$E$37+Inputs!$E$38</f>
         <v>2020</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D35" s="18" t="s">
         <v>84</v>
@@ -33613,59 +33934,59 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B36" s="27" t="n">
         <f aca="false">(B11+B26)*B35/10</f>
         <v>12120</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B37" s="27" t="n">
         <f aca="false">B15+B23+B30</f>
         <v>3676.30454976</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B38" s="27" t="n">
         <f aca="false">FM_Base!$G$42/10000</f>
         <v>91.490638</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B39" s="26" t="n">
         <f aca="false">FM_Base!$G$9/((B13+B21+B28)*1000)</f>
@@ -33675,7 +33996,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="E39" s="12"/>
     </row>
@@ -33705,56 +34026,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>34</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33816,7 +34137,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B6" s="20" t="n">
         <f aca="false">Inputs!$E$37*0.8</f>
@@ -33873,7 +34194,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B7" s="20" t="n">
         <f aca="false">Inputs!$E$37*1.2</f>
@@ -33930,7 +34251,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -33987,7 +34308,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34044,7 +34365,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34101,7 +34422,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34158,7 +34479,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34215,7 +34536,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34272,7 +34593,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34329,7 +34650,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34386,7 +34707,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34443,7 +34764,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34500,7 +34821,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34557,7 +34878,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34614,7 +34935,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34671,7 +34992,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34728,7 +35049,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B22" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34785,7 +35106,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B23" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34842,7 +35163,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B24" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34899,7 +35220,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B25" s="11" t="n">
         <f aca="false">Inputs!$E$37</f>
@@ -34956,18 +35277,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -34981,7 +35302,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B30" s="17" t="n">
         <v>230691.8</v>
@@ -34989,7 +35310,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B31" s="17" t="n">
         <v>-142696.2</v>
@@ -35000,7 +35321,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B32" s="17" t="n">
         <v>-81695.7</v>
@@ -35011,7 +35332,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B33" s="17" t="n">
         <v>-46636.7</v>
@@ -35022,7 +35343,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B34" s="17" t="n">
         <v>-33169.3</v>
@@ -35033,7 +35354,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B35" s="17" t="n">
         <v>-30175</v>
@@ -35044,7 +35365,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B36" s="17" t="n">
         <v>-13965.8</v>
@@ -35055,7 +35376,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B37" s="17" t="n">
         <v>-16468.6</v>
@@ -35066,7 +35387,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B38" s="17" t="n">
         <v>-13200</v>
@@ -35077,7 +35398,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B39" s="17" t="n">
         <v>-9384.1</v>
@@ -35088,7 +35409,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B40" s="17" t="n">
         <v>-7675.2</v>
@@ -35099,7 +35420,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B41" s="17" t="n">
         <v>-1296.7</v>
@@ -35141,12 +35462,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35154,54 +35475,54 @@
         <v>48</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>1</v>
@@ -35216,7 +35537,7 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I5" s="27" t="n">
         <f aca="false">IF(D5&lt;=12,13-D5,0)*F5</f>
@@ -35245,13 +35566,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>1</v>
@@ -35266,7 +35587,7 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I6" s="27" t="n">
         <f aca="false">IF(D6&lt;=12,13-D6,0)*F6</f>
@@ -35295,13 +35616,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>1</v>
@@ -35316,7 +35637,7 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">IF(D7&lt;=12,13-D7,0)*F7</f>
@@ -35345,13 +35666,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>2</v>
@@ -35366,7 +35687,7 @@
         <v>0.5</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I8" s="27" t="n">
         <f aca="false">IF(D8&lt;=12,13-D8,0)*F8</f>
@@ -35395,13 +35716,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>657</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>653</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>2</v>
@@ -35416,7 +35737,7 @@
         <v>0.6</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I9" s="27" t="n">
         <f aca="false">IF(D9&lt;=12,13-D9,0)*F9</f>
@@ -35445,13 +35766,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>4</v>
@@ -35466,7 +35787,7 @@
         <v>0.5</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I10" s="27" t="n">
         <f aca="false">IF(D10&lt;=12,13-D10,0)*F10</f>
@@ -35495,13 +35816,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>6</v>
@@ -35516,7 +35837,7 @@
         <v>0.5</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I11" s="27" t="n">
         <f aca="false">IF(D11&lt;=12,13-D11,0)*F11</f>
@@ -35545,13 +35866,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>7</v>
@@ -35566,7 +35887,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I12" s="27" t="n">
         <f aca="false">IF(D12&lt;=12,13-D12,0)*F12</f>
@@ -35595,13 +35916,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D13" s="17" t="n">
         <v>10</v>
@@ -35616,7 +35937,7 @@
         <v>0.5</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I13" s="27" t="n">
         <f aca="false">IF(D13&lt;=12,13-D13,0)*F13</f>
@@ -35645,13 +35966,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>10</v>
@@ -35666,7 +35987,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I14" s="27" t="n">
         <f aca="false">IF(D14&lt;=12,13-D14,0)*F14</f>
@@ -35695,13 +36016,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>13</v>
@@ -35716,7 +36037,7 @@
         <v>0.4</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="I15" s="27" t="n">
         <f aca="false">IF(D15&lt;=12,13-D15,0)*F15</f>
@@ -35745,13 +36066,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>13</v>
@@ -35766,7 +36087,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I16" s="27" t="n">
         <f aca="false">IF(D16&lt;=12,13-D16,0)*F16</f>
@@ -35795,13 +36116,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D17" s="17" t="n">
         <v>16</v>
@@ -35816,7 +36137,7 @@
         <v>0.4</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I17" s="27" t="n">
         <f aca="false">IF(D17&lt;=12,13-D17,0)*F17</f>
@@ -35845,13 +36166,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>680</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>676</v>
       </c>
       <c r="D18" s="17" t="n">
         <v>19</v>
@@ -35866,7 +36187,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I18" s="27" t="n">
         <f aca="false">IF(D18&lt;=12,13-D18,0)*F18</f>
@@ -35924,7 +36245,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="10" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I20" s="31" t="n">
         <f aca="false">I19/12</f>
@@ -35937,7 +36258,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="10" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="K21" s="27" t="n">
         <f aca="false">FM_Base!$C$67-K19</f>
@@ -35951,7 +36272,7 @@
     <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -35965,29 +36286,29 @@
         <v>510</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>4800</v>
@@ -36014,15 +36335,15 @@
         <v>1280</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="E25" s="17" t="n">
         <v>6000</v>
@@ -36049,15 +36370,15 @@
         <v>3600</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>5000</v>
@@ -36084,15 +36405,15 @@
         <v>2000</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E27" s="17" t="n">
         <v>2500</v>
@@ -36119,15 +36440,15 @@
         <v>2400</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E28" s="17" t="n">
         <v>0</v>
@@ -36154,15 +36475,15 @@
         <v>0</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="E29" s="17" t="n">
         <v>2000</v>
@@ -36189,15 +36510,15 @@
         <v>0</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>1500</v>
@@ -36224,15 +36545,15 @@
         <v>2025</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>1500</v>
@@ -36259,15 +36580,15 @@
         <v>2400</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>4800</v>
@@ -36294,15 +36615,15 @@
         <v>0</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E33" s="17" t="n">
         <v>4000</v>
@@ -36329,12 +36650,12 @@
         <v>0</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="25" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E34" s="30" t="n">
         <f aca="false">SUM(E24:E33)</f>
@@ -36359,7 +36680,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="10" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="E35" s="24" t="n">
         <f aca="false">E34*0.1</f>
@@ -36376,7 +36697,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="10" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E36" s="24" t="n">
         <f aca="false">SUMIF($C$5:$C$18,"R&amp;D",M$5:M$18)*0.05</f>
@@ -36393,7 +36714,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="10" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="E37" s="27" t="n">
         <f aca="false">FM_Base!$C$68-(E34+E35+E36)</f>
@@ -36407,15 +36728,15 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8"/>
       <c r="B39" s="8" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>510</v>
@@ -36425,14 +36746,14 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="9" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="10" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E40" s="24" t="n">
         <f aca="false">SUMIF($C$5:$C$18,"R&amp;D",M$5:M$18)</f>
@@ -36447,12 +36768,12 @@
         <v>53175</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="10" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E41" s="24" t="n">
         <f aca="false">SUMIF($C$5:$C$18,"Founder",M$5:M$18)</f>
@@ -36467,12 +36788,12 @@
         <v>13200</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="10" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E42" s="24" t="n">
         <f aca="false">SUMIF($L$24:$L$33,"연구재료비",J$24:J$33)</f>
@@ -36487,12 +36808,12 @@
         <v>20120</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="10" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E43" s="24" t="n">
         <f aca="false">SUMIF($L$24:$L$33,"연구활동비",J$24:J$33)</f>
@@ -36507,12 +36828,12 @@
         <v>11525</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="10" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E44" s="24" t="n">
         <f aca="false">E36</f>
@@ -36527,12 +36848,12 @@
         <v>2658.75</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="25" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E45" s="30" t="n">
         <f aca="false">SUM(E40:E44)</f>
@@ -36549,7 +36870,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="10" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E46" s="24" t="n">
         <f aca="false">G47*E45/G45-E45</f>
@@ -36566,7 +36887,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="18" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E47" s="30" t="n">
         <f aca="false">E45+E46</f>
@@ -36583,19 +36904,19 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="10" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="G48" s="24" t="n">
         <f aca="false">Inputs!$E$84</f>
         <v>80000</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="10" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G49" s="24" t="n">
         <f aca="false">G47-Inputs!$E$84</f>
@@ -36605,7 +36926,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="10" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G50" s="24" t="n">
         <f aca="false">G41</f>
@@ -36615,44 +36936,44 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="10" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G51" s="24" t="n">
         <f aca="false">G47-Inputs!$E$84-G41</f>
         <v>13466.6666666667</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="10" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G52" s="24" t="n">
         <f aca="false">IF((G47-Inputs!$E$84-G41)/(G47-Inputs!$E$84)&gt;=Inputs!$E$87-0.0001,1,0)</f>
         <v>1</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="10" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G53" s="26" t="n">
         <f aca="false">G46/(G45-G41)</f>
         <v>0.0684499568942934</v>
       </c>
       <c r="L53" s="10" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8"/>
       <c r="B55" s="8" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -36670,14 +36991,14 @@
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="9" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="25" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="E56" s="30" t="n">
         <f aca="false">-FM_Base!$C$71</f>
@@ -36694,7 +37015,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="10" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="E57" s="24" t="n">
         <f aca="false">E56-FM_Base!$C$69</f>
@@ -36711,7 +37032,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="12" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="E58" s="24" t="n">
         <f aca="false">E47*Inputs!$E$86</f>
@@ -36728,7 +37049,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="12" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G59" s="24" t="n">
         <f aca="false">F56/12*3</f>
@@ -36737,7 +37058,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="18" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="G60" s="32" t="n">
         <f aca="false">G56-G58+G59</f>
@@ -36746,35 +37067,35 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="12" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>137770.1</v>
       </c>
       <c r="L61" s="12" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="12" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G62" s="17" t="n">
         <v>215241.1</v>
       </c>
       <c r="L62" s="10" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="12" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>20000</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -36804,7 +37125,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36815,738 +37136,738 @@
         <v>512</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="63.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="108.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="141.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="101.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="63.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="63.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="71.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="87.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="63.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="108.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="170.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="170.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
   </sheetData>
@@ -39296,18 +39617,18 @@
         <v>200</v>
       </c>
       <c r="G26" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>33</v>
@@ -39325,12 +39646,12 @@
         <v>84</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -39342,13 +39663,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="C29" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="D29" s="20" t="n">
         <v>1.5</v>
@@ -39363,18 +39684,18 @@
         <v>55</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="C30" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>40</v>
@@ -39389,15 +39710,15 @@
         <v>84</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>33</v>
@@ -39415,18 +39736,18 @@
         <v>84</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="C32" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>1400</v>
@@ -39441,12 +39762,12 @@
         <v>84</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -39458,13 +39779,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="C34" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="D34" s="21" t="n">
         <v>400</v>
@@ -39479,18 +39800,18 @@
         <v>84</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>146</v>
-      </c>
       <c r="C35" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D35" s="17" t="n">
         <v>200</v>
@@ -39505,18 +39826,18 @@
         <v>84</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>149</v>
-      </c>
       <c r="C36" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>150</v>
@@ -39531,18 +39852,18 @@
         <v>84</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="C37" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="D37" s="21" t="n">
         <v>1290</v>
@@ -39557,18 +39878,18 @@
         <v>84</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="C38" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D38" s="17" t="n">
         <v>80</v>
@@ -39586,13 +39907,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="C39" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D39" s="17" t="n">
         <v>120</v>
@@ -39610,13 +39931,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="C40" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>29</v>
@@ -39631,18 +39952,18 @@
         <v>84</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="C41" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="D41" s="17" t="n">
         <v>60</v>
@@ -39660,13 +39981,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="C42" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="D42" s="21" t="n">
         <v>42</v>
@@ -39681,18 +40002,18 @@
         <v>84</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>171</v>
-      </c>
       <c r="C43" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D43" s="17" t="n">
         <v>72</v>
@@ -39707,18 +40028,18 @@
         <v>84</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="C44" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="D44" s="20" t="n">
         <v>4.5</v>
@@ -39733,18 +40054,18 @@
         <v>84</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="C45" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="D45" s="20" t="n">
         <v>4</v>
@@ -39759,18 +40080,18 @@
         <v>84</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>182</v>
-      </c>
       <c r="C46" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D46" s="20" t="n">
         <v>2.5</v>
@@ -39788,13 +40109,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>184</v>
-      </c>
       <c r="C47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D47" s="20" t="n">
         <v>4</v>
@@ -39812,13 +40133,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B48" s="12" t="s">
-        <v>186</v>
-      </c>
       <c r="C48" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D48" s="20" t="n">
         <v>4</v>
@@ -39836,13 +40157,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="C49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D49" s="20" t="n">
         <v>2</v>
@@ -39860,10 +40181,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>189</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>190</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>33</v>
@@ -39884,10 +40205,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" s="12" t="s">
         <v>191</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>192</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>33</v>
@@ -39908,13 +40229,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="C52" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="D52" s="17" t="n">
         <v>60</v>
@@ -39929,15 +40250,15 @@
         <v>84</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B53" s="12" t="s">
         <v>197</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>198</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>33</v>
@@ -39958,13 +40279,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>200</v>
-      </c>
       <c r="C54" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54" s="17" t="n">
         <v>80</v>
@@ -39979,15 +40300,15 @@
         <v>84</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>203</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>33</v>
@@ -40008,10 +40329,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>33</v>
@@ -40029,18 +40350,18 @@
         <v>84</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B57" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>208</v>
-      </c>
       <c r="C57" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D57" s="20" t="n">
         <v>6</v>
@@ -40058,7 +40379,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -40070,13 +40391,13 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B59" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>211</v>
-      </c>
       <c r="C59" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D59" s="17" t="n">
         <v>200</v>
@@ -40091,18 +40412,18 @@
         <v>84</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="C60" s="12" t="s">
         <v>214</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>215</v>
       </c>
       <c r="D60" s="20" t="n">
         <v>1.6</v>
@@ -40120,13 +40441,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B61" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>217</v>
-      </c>
       <c r="C61" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D61" s="17" t="n">
         <v>100</v>
@@ -40144,13 +40465,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B62" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>219</v>
-      </c>
       <c r="C62" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D62" s="17" t="n">
         <v>145</v>
@@ -40168,13 +40489,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="C63" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D63" s="17" t="n">
         <v>70</v>
@@ -40189,18 +40510,18 @@
         <v>84</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B64" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>224</v>
-      </c>
       <c r="C64" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D64" s="17" t="n">
         <v>25</v>
@@ -40218,10 +40539,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B65" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>226</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>33</v>
@@ -40239,18 +40560,18 @@
         <v>84</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="C66" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="D66" s="20" t="n">
         <v>0.9</v>
@@ -40268,13 +40589,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="C67" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="D67" s="17" t="n">
         <v>18</v>
@@ -40292,13 +40613,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B68" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="C68" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="D68" s="17" t="n">
         <v>4</v>
@@ -40316,10 +40637,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B69" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>238</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>33</v>
@@ -40340,10 +40661,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>239</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>240</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>33</v>
@@ -40364,10 +40685,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>241</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>242</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>33</v>
@@ -40388,10 +40709,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>243</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>244</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>33</v>
@@ -40412,13 +40733,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>246</v>
-      </c>
       <c r="C73" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D73" s="17" t="n">
         <v>180</v>
@@ -40436,13 +40757,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="C74" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>249</v>
       </c>
       <c r="D74" s="17" t="n">
         <v>2000</v>
@@ -40460,10 +40781,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>251</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>33</v>
@@ -40481,18 +40802,18 @@
         <v>84</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B76" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="C76" s="12" t="s">
         <v>254</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>255</v>
       </c>
       <c r="D76" s="19" t="n">
         <v>0.08</v>
@@ -40507,18 +40828,18 @@
         <v>84</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B77" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>258</v>
-      </c>
       <c r="C77" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D77" s="17" t="n">
         <v>36</v>
@@ -40533,12 +40854,12 @@
         <v>84</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
@@ -40550,13 +40871,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="B79" s="12" t="s">
-        <v>262</v>
-      </c>
       <c r="C79" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D79" s="19" t="n">
         <v>0.05</v>
@@ -40574,10 +40895,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>263</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>264</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>39</v>
@@ -40598,10 +40919,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B81" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>33</v>
@@ -40622,10 +40943,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B82" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>268</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>33</v>
@@ -40646,7 +40967,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
@@ -40658,13 +40979,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B84" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="B84" s="12" t="s">
-        <v>271</v>
-      </c>
       <c r="C84" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D84" s="17" t="n">
         <v>80000</v>
@@ -40679,18 +41000,18 @@
         <v>55</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B85" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B85" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="C85" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D85" s="17" t="n">
         <v>24</v>
@@ -40705,15 +41026,15 @@
         <v>55</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="B86" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>33</v>
@@ -40731,15 +41052,15 @@
         <v>55</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B87" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>33</v>
@@ -40757,18 +41078,18 @@
         <v>55</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B88" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B88" s="12" t="s">
-        <v>283</v>
-      </c>
       <c r="C88" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D88" s="17" t="n">
         <v>20000</v>
@@ -40783,18 +41104,18 @@
         <v>55</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B89" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B89" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="C89" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D89" s="17" t="n">
         <v>15000</v>
@@ -40809,7 +41130,7 @@
         <v>55</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -40842,7 +41163,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40856,7 +41177,7 @@
         <v>23</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>24</v>
@@ -40882,10 +41203,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>291</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>33</v>
@@ -40912,15 +41233,15 @@
         <v>84</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>291</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>33</v>
@@ -40947,15 +41268,15 @@
         <v>84</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>291</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>33</v>
@@ -40982,15 +41303,15 @@
         <v>84</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>293</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>294</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>33</v>
@@ -41014,18 +41335,18 @@
         <v>0.65</v>
       </c>
       <c r="J8" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="K8" s="12" t="s">
         <v>295</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>293</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>294</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>33</v>
@@ -41049,18 +41370,18 @@
         <v>0.8</v>
       </c>
       <c r="J9" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="K9" s="12" t="s">
         <v>295</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>293</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>294</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>33</v>
@@ -41084,21 +41405,21 @@
         <v>0.85</v>
       </c>
       <c r="J10" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>295</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>298</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>22</v>
@@ -41122,18 +41443,18 @@
         <v>84</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>298</v>
-      </c>
       <c r="C13" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>45</v>
@@ -41157,18 +41478,18 @@
         <v>84</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>298</v>
-      </c>
       <c r="C14" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>46</v>
@@ -41192,18 +41513,18 @@
         <v>84</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>301</v>
-      </c>
       <c r="C16" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>22</v>
@@ -41227,18 +41548,18 @@
         <v>84</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>301</v>
-      </c>
       <c r="C17" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>45</v>
@@ -41262,18 +41583,18 @@
         <v>84</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>301</v>
-      </c>
       <c r="C18" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>46</v>
@@ -41297,18 +41618,18 @@
         <v>84</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>304</v>
-      </c>
       <c r="C20" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>22</v>
@@ -41332,18 +41653,18 @@
         <v>84</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>304</v>
-      </c>
       <c r="C21" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>45</v>
@@ -41367,18 +41688,18 @@
         <v>84</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>304</v>
-      </c>
       <c r="C22" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>46</v>
@@ -41402,18 +41723,18 @@
         <v>84</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>307</v>
-      </c>
       <c r="C24" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>22</v>
@@ -41437,18 +41758,18 @@
         <v>84</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>307</v>
-      </c>
       <c r="C25" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>45</v>
@@ -41472,18 +41793,18 @@
         <v>84</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>307</v>
-      </c>
       <c r="C26" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>46</v>
@@ -41507,18 +41828,18 @@
         <v>84</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>310</v>
-      </c>
       <c r="C28" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>22</v>
@@ -41542,18 +41863,18 @@
         <v>84</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>310</v>
-      </c>
       <c r="C29" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>45</v>
@@ -41577,18 +41898,18 @@
         <v>84</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>310</v>
-      </c>
       <c r="C30" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>46</v>
@@ -41612,15 +41933,15 @@
         <v>84</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>39</v>
@@ -41644,18 +41965,18 @@
         <v>40</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>39</v>
@@ -41679,18 +42000,18 @@
         <v>60</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>39</v>
@@ -41714,18 +42035,18 @@
         <v>70</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>315</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>316</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>39</v>
@@ -41749,18 +42070,18 @@
         <v>150</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>315</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>316</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>39</v>
@@ -41784,18 +42105,18 @@
         <v>340</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>315</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>316</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>39</v>
@@ -41819,18 +42140,18 @@
         <v>600</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>39</v>
@@ -41854,18 +42175,18 @@
         <v>40</v>
       </c>
       <c r="J40" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>39</v>
@@ -41889,18 +42210,18 @@
         <v>80</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>39</v>
@@ -41924,18 +42245,18 @@
         <v>120</v>
       </c>
       <c r="J42" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>322</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>33</v>
@@ -41962,15 +42283,15 @@
         <v>84</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>322</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>33</v>
@@ -41997,15 +42318,15 @@
         <v>84</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>322</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>33</v>
@@ -42032,15 +42353,15 @@
         <v>84</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>324</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>325</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>33</v>
@@ -42070,10 +42391,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>324</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>325</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>33</v>
@@ -42103,10 +42424,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>324</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>325</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>33</v>
@@ -42136,13 +42457,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="C52" s="12" t="s">
         <v>327</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>328</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>22</v>
@@ -42169,13 +42490,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B53" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="C53" s="12" t="s">
         <v>327</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>328</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>45</v>
@@ -42202,13 +42523,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B54" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="C54" s="12" t="s">
         <v>327</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>328</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>46</v>
@@ -42235,13 +42556,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="C56" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>22</v>
@@ -42262,21 +42583,21 @@
         <v>2</v>
       </c>
       <c r="J56" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="C57" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>45</v>
@@ -42297,21 +42618,21 @@
         <v>3</v>
       </c>
       <c r="J57" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="C58" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>46</v>
@@ -42332,21 +42653,21 @@
         <v>4</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="C60" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>335</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>22</v>
@@ -42370,18 +42691,18 @@
         <v>84</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="C61" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>335</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>45</v>
@@ -42405,18 +42726,18 @@
         <v>84</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B62" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="C62" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>335</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>46</v>
@@ -42440,18 +42761,18 @@
         <v>84</v>
       </c>
       <c r="K62" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>338</v>
-      </c>
       <c r="C64" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>22</v>
@@ -42475,18 +42796,18 @@
         <v>84</v>
       </c>
       <c r="K64" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>338</v>
-      </c>
       <c r="C65" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>45</v>
@@ -42510,18 +42831,18 @@
         <v>84</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B66" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>338</v>
-      </c>
       <c r="C66" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>46</v>
@@ -42545,18 +42866,18 @@
         <v>84</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B68" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>341</v>
-      </c>
       <c r="C68" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>22</v>
@@ -42583,13 +42904,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B69" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>341</v>
-      </c>
       <c r="C69" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>45</v>
@@ -42616,13 +42937,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>341</v>
-      </c>
       <c r="C70" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>46</v>
@@ -42649,13 +42970,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="B72" s="12" t="s">
-        <v>343</v>
-      </c>
       <c r="C72" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D72" s="12" t="s">
         <v>22</v>
@@ -42682,13 +43003,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="B73" s="12" t="s">
-        <v>343</v>
-      </c>
       <c r="C73" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>45</v>
@@ -42715,13 +43036,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B74" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>343</v>
-      </c>
       <c r="C74" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>46</v>
@@ -42748,13 +43069,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B76" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B76" s="12" t="s">
-        <v>345</v>
-      </c>
       <c r="C76" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D76" s="12" t="s">
         <v>22</v>
@@ -42781,13 +43102,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B77" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>345</v>
-      </c>
       <c r="C77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>45</v>
@@ -42814,13 +43135,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B78" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="B78" s="12" t="s">
-        <v>345</v>
-      </c>
       <c r="C78" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>46</v>
@@ -42847,13 +43168,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="B80" s="12" t="s">
-        <v>347</v>
-      </c>
       <c r="C80" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>22</v>
@@ -42880,13 +43201,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B81" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="B81" s="12" t="s">
-        <v>347</v>
-      </c>
       <c r="C81" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D81" s="12" t="s">
         <v>45</v>
@@ -42913,13 +43234,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B82" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="B82" s="12" t="s">
-        <v>347</v>
-      </c>
       <c r="C82" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>46</v>
@@ -42946,13 +43267,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B84" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="B84" s="12" t="s">
-        <v>349</v>
-      </c>
       <c r="C84" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>22</v>
@@ -42979,13 +43300,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B85" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="B85" s="12" t="s">
-        <v>349</v>
-      </c>
       <c r="C85" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>45</v>
@@ -43012,13 +43333,13 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>349</v>
-      </c>
       <c r="C86" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>46</v>
@@ -43045,13 +43366,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B88" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="B88" s="12" t="s">
-        <v>351</v>
-      </c>
       <c r="C88" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>22</v>
@@ -43078,13 +43399,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B89" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="B89" s="12" t="s">
-        <v>351</v>
-      </c>
       <c r="C89" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>45</v>
@@ -43111,13 +43432,13 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B90" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="B90" s="12" t="s">
-        <v>351</v>
-      </c>
       <c r="C90" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>46</v>
@@ -43144,13 +43465,13 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B92" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B92" s="12" t="s">
-        <v>353</v>
-      </c>
       <c r="C92" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>22</v>
@@ -43174,18 +43495,18 @@
         <v>84</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B93" s="12" t="s">
-        <v>353</v>
-      </c>
       <c r="C93" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>45</v>
@@ -43209,18 +43530,18 @@
         <v>84</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B94" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B94" s="12" t="s">
-        <v>353</v>
-      </c>
       <c r="C94" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>46</v>
@@ -43244,18 +43565,18 @@
         <v>84</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B96" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B96" s="12" t="s">
-        <v>356</v>
-      </c>
       <c r="C96" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>22</v>
@@ -43282,13 +43603,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B97" s="12" t="s">
-        <v>356</v>
-      </c>
       <c r="C97" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>45</v>
@@ -43315,13 +43636,13 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>356</v>
-      </c>
       <c r="C98" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D98" s="12" t="s">
         <v>46</v>
@@ -43348,13 +43669,13 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B100" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B100" s="12" t="s">
-        <v>358</v>
-      </c>
       <c r="C100" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D100" s="12" t="s">
         <v>22</v>
@@ -43381,13 +43702,13 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B101" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B101" s="12" t="s">
-        <v>358</v>
-      </c>
       <c r="C101" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D101" s="12" t="s">
         <v>45</v>
@@ -43414,13 +43735,13 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B102" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B102" s="12" t="s">
-        <v>358</v>
-      </c>
       <c r="C102" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>46</v>
@@ -43447,13 +43768,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B104" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B104" s="12" t="s">
-        <v>360</v>
-      </c>
       <c r="C104" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D104" s="12" t="s">
         <v>22</v>
@@ -43480,13 +43801,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B105" s="12" t="s">
-        <v>360</v>
-      </c>
       <c r="C105" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D105" s="12" t="s">
         <v>45</v>
@@ -43513,13 +43834,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B106" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B106" s="12" t="s">
-        <v>360</v>
-      </c>
       <c r="C106" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D106" s="12" t="s">
         <v>46</v>
@@ -43546,13 +43867,13 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B108" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B108" s="10" t="s">
-        <v>362</v>
-      </c>
       <c r="C108" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D108" s="12" t="s">
         <v>22</v>
@@ -43573,7 +43894,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="K108" s="12" t="s">
         <v>363</v>
@@ -43581,13 +43902,13 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B109" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B109" s="10" t="s">
-        <v>362</v>
-      </c>
       <c r="C109" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D109" s="12" t="s">
         <v>45</v>
@@ -43608,7 +43929,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="K109" s="12" t="s">
         <v>363</v>
@@ -43616,13 +43937,13 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B110" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B110" s="10" t="s">
-        <v>362</v>
-      </c>
       <c r="C110" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D110" s="12" t="s">
         <v>46</v>
@@ -43643,7 +43964,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="K110" s="12" t="s">
         <v>363</v>
@@ -43657,7 +43978,7 @@
         <v>365</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D112" s="12" t="s">
         <v>22</v>
@@ -43678,7 +43999,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="K112" s="12" t="s">
         <v>366</v>
@@ -43692,7 +44013,7 @@
         <v>365</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D113" s="12" t="s">
         <v>45</v>
@@ -43713,7 +44034,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="K113" s="12" t="s">
         <v>366</v>
@@ -43727,7 +44048,7 @@
         <v>365</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D114" s="12" t="s">
         <v>46</v>
@@ -43748,7 +44069,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="18" t="s">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="K114" s="12" t="s">
         <v>366</v>
@@ -43817,7 +44138,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -44176,7 +44497,7 @@
         <v>381</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$52</f>
@@ -44624,7 +44945,7 @@
         <v>396</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">Inputs!$D$44*Inputs!$D$45+Inputs!$D$46*Inputs!$D$47+Inputs!$D$48*Inputs!$D$49</f>
@@ -44652,7 +44973,7 @@
         <v>397</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="14" t="n">
         <f aca="false">Inputs!$D$46*Inputs!$D$47+Inputs!$D$48*Inputs!$D$49</f>
@@ -44680,7 +45001,7 @@
         <v>398</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">Inputs!$D$44*Inputs!$D$45</f>
@@ -44708,7 +45029,7 @@
         <v>399</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C35" s="24" t="n">
         <f aca="false">(C5+C6)*Inputs!$D$34*C31+C8*Inputs!$D$35+C7*Inputs!$D$36*C31</f>
@@ -44740,7 +45061,7 @@
         <v>400</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C36" s="24" t="n">
         <f aca="false">(C14-C7)*Inputs!$D$38*C31+C7*Inputs!$D$39*C31</f>
@@ -44772,7 +45093,7 @@
         <v>401</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C37" s="24" t="n">
         <f aca="false">C18*Inputs!$D$37*C31+C20*Inputs!$D$37*Inputs!$D$56</f>
@@ -44804,7 +45125,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C38" s="24" t="n">
         <f aca="false">C25*Inputs!$D$40*12</f>
@@ -44836,7 +45157,7 @@
         <v>403</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" s="24" t="n">
         <f aca="false">C23*Inputs!$D$51*Inputs!$D$42+C27*Inputs!$D$57*12</f>
@@ -44868,7 +45189,7 @@
         <v>404</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C40" s="24" t="n">
         <f aca="false">C23*Inputs!$D$50*C32+(C25+C27)*Inputs!$D$50*C33</f>
@@ -44900,7 +45221,7 @@
         <v>405</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C41" s="24" t="n">
         <f aca="false">0*Inputs!$D$53*Inputs!$D$52+0*Inputs!$D$55*Inputs!$D$54</f>
@@ -44932,7 +45253,7 @@
         <v>406</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C42" s="24" t="n">
         <f aca="false">SUM(C35:C41)</f>
@@ -44973,7 +45294,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>33</v>
@@ -45004,7 +45325,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C45" s="14" t="n">
         <f aca="false">Inputs!$D$59*(C44+Inputs!$D$60*(1-C44))+Inputs!$D$61*(1-C44)</f>
@@ -45032,7 +45353,7 @@
         <v>409</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C46" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$12</f>
@@ -45060,7 +45381,7 @@
         <v>410</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C47" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$24*Inputs_Yearly!$E$28+Inputs!$D$66*Inputs!$D$67+Inputs!$D$68</f>
@@ -45088,7 +45409,7 @@
         <v>411</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C48" s="24" t="n">
         <f aca="false">(C5+C6)*C45+C8*Inputs!$D$62+C7*Inputs!$D$63</f>
@@ -45120,7 +45441,7 @@
         <v>412</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C49" s="24" t="n">
         <f aca="false">(C5+C6+C8+C7)*Inputs!$D$64</f>
@@ -45152,7 +45473,7 @@
         <v>413</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C50" s="24" t="n">
         <f aca="false">(C18+C20)*C46</f>
@@ -45184,7 +45505,7 @@
         <v>414</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C51" s="24" t="n">
         <f aca="false">(C14-C7)*Inputs_Yearly!$E$16+C7*Inputs_Yearly!$E$20</f>
@@ -45216,7 +45537,7 @@
         <v>415</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C52" s="14" t="n">
         <f aca="false">Inputs!$D$65*C37</f>
@@ -45248,7 +45569,7 @@
         <v>416</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C53" s="24" t="n">
         <f aca="false">C19*C46</f>
@@ -45280,7 +45601,7 @@
         <v>417</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">0+C53</f>
@@ -45308,7 +45629,7 @@
         <v>418</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">0*(1-Inputs!$D$75)/5+C53*(1-Inputs!$D$75)/5*0.5</f>
@@ -45340,7 +45661,7 @@
         <v>419</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C56" s="24" t="n">
         <f aca="false">(C23*Inputs!$D$51+C25+C27)*C47</f>
@@ -45372,7 +45693,7 @@
         <v>420</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C57" s="24" t="n">
         <f aca="false">C40*Inputs!$D$69+(C25+C27)*C34*Inputs!$D$69</f>
@@ -45404,7 +45725,7 @@
         <v>421</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C58" s="24" t="n">
         <f aca="false">0*Inputs!$D$53*Inputs!$D$52*Inputs!$D$70+0*Inputs!$D$55*Inputs!$D$54*Inputs!$D$71</f>
@@ -45436,7 +45757,7 @@
         <v>422</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C59" s="24" t="n">
         <f aca="false">C48+C49+C50+C51+C52+C55+C56+C57+C58</f>
@@ -45468,7 +45789,7 @@
         <v>31</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C60" s="24" t="n">
         <f aca="false">C42-C59</f>
@@ -45540,7 +45861,7 @@
         <v>424</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="14" t="n">
         <f aca="false">Inputs!$D$72*(C6*(Inputs!$D$34*C31+C10*(Inputs!$D$37+Inputs!$D$38)*C31)+C7*(Inputs!$D$36+Inputs!$D$37+Inputs!$D$39)*C31)</f>
@@ -45572,7 +45893,7 @@
         <v>425</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="24" t="n">
         <f aca="false">C5*Inputs!$D$73</f>
@@ -45604,7 +45925,7 @@
         <v>426</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C65" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$56*Inputs!$D$74</f>
@@ -45636,7 +45957,7 @@
         <v>427</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C66" s="24" t="n">
         <f aca="false">C60-C63-C64-C65</f>
@@ -45668,7 +45989,7 @@
         <v>428</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C67" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$60*Inputs_Yearly!$E$64</f>
@@ -45700,7 +46021,7 @@
         <v>429</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C68" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$68+Inputs_Yearly!$E$72+Inputs_Yearly!$E$76+Inputs_Yearly!$E$80+Inputs_Yearly!$E$84+Inputs_Yearly!$E$88+Inputs_Yearly!$E$92+Inputs_Yearly!$E$96+Inputs_Yearly!$E$100+Inputs_Yearly!$E$104+Inputs_Yearly!$E$108+Inputs_Yearly!$E$112</f>
@@ -45732,7 +46053,7 @@
         <v>430</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C69" s="24" t="n">
         <f aca="false">C67+C68</f>
@@ -45764,7 +46085,7 @@
         <v>431</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C70" s="24" t="n">
         <f aca="false">C66-C69</f>
@@ -45796,7 +46117,7 @@
         <v>432</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C71" s="24" t="n">
         <f aca="false">C70+C55-C53</f>
@@ -45828,7 +46149,7 @@
         <v>37</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C72" s="24" t="n">
         <f aca="false">0+C71</f>
@@ -45868,7 +46189,7 @@
         <v>434</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C74" s="24" t="n">
         <f aca="false">C35+C36+C37</f>
@@ -45900,7 +46221,7 @@
         <v>435</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C75" s="24" t="n">
         <f aca="false">C35+C36</f>
@@ -45932,7 +46253,7 @@
         <v>436</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C76" s="24" t="n">
         <f aca="false">C38+C39+C40</f>
@@ -45964,7 +46285,7 @@
         <v>437</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C77" s="24" t="n">
         <f aca="false">C41</f>
@@ -46110,7 +46431,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -46469,7 +46790,7 @@
         <v>381</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$53</f>
@@ -46917,7 +47238,7 @@
         <v>396</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">Inputs!$E$44*Inputs!$E$45+Inputs!$E$46*Inputs!$E$47+Inputs!$E$48*Inputs!$E$49</f>
@@ -46945,7 +47266,7 @@
         <v>397</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="14" t="n">
         <f aca="false">Inputs!$E$46*Inputs!$E$47+Inputs!$E$48*Inputs!$E$49</f>
@@ -46973,7 +47294,7 @@
         <v>398</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">Inputs!$E$44*Inputs!$E$45</f>
@@ -47001,7 +47322,7 @@
         <v>399</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C35" s="24" t="n">
         <f aca="false">(C5+C6)*Inputs!$E$34*C31+C8*Inputs!$E$35+C7*Inputs!$E$36*C31</f>
@@ -47033,7 +47354,7 @@
         <v>400</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C36" s="24" t="n">
         <f aca="false">(C14-C7)*Inputs!$E$38*C31+C7*Inputs!$E$39*C31</f>
@@ -47065,7 +47386,7 @@
         <v>401</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C37" s="24" t="n">
         <f aca="false">C18*Inputs!$E$37*C31+C20*Inputs!$E$37*Inputs!$E$56</f>
@@ -47097,7 +47418,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C38" s="24" t="n">
         <f aca="false">C25*Inputs!$E$40*12</f>
@@ -47129,7 +47450,7 @@
         <v>403</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" s="24" t="n">
         <f aca="false">C23*Inputs!$E$51*Inputs!$E$42+C27*Inputs!$E$57*12</f>
@@ -47161,7 +47482,7 @@
         <v>404</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C40" s="24" t="n">
         <f aca="false">C23*Inputs!$E$50*C32+(C25+C27)*Inputs!$E$50*C33</f>
@@ -47193,7 +47514,7 @@
         <v>405</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C41" s="24" t="n">
         <f aca="false">0*Inputs!$E$53*Inputs!$E$52+0*Inputs!$E$55*Inputs!$E$54</f>
@@ -47225,7 +47546,7 @@
         <v>406</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C42" s="24" t="n">
         <f aca="false">SUM(C35:C41)</f>
@@ -47266,7 +47587,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>33</v>
@@ -47297,7 +47618,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C45" s="14" t="n">
         <f aca="false">Inputs!$E$59*(C44+Inputs!$E$60*(1-C44))+Inputs!$E$61*(1-C44)</f>
@@ -47325,7 +47646,7 @@
         <v>409</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C46" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$13</f>
@@ -47353,7 +47674,7 @@
         <v>410</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C47" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$25*Inputs_Yearly!$E$29+Inputs!$E$66*Inputs!$E$67+Inputs!$E$68</f>
@@ -47381,7 +47702,7 @@
         <v>411</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C48" s="24" t="n">
         <f aca="false">(C5+C6)*C45+C8*Inputs!$E$62+C7*Inputs!$E$63</f>
@@ -47413,7 +47734,7 @@
         <v>412</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C49" s="24" t="n">
         <f aca="false">(C5+C6+C8+C7)*Inputs!$E$64</f>
@@ -47445,7 +47766,7 @@
         <v>413</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C50" s="24" t="n">
         <f aca="false">(C18+C20)*C46</f>
@@ -47477,7 +47798,7 @@
         <v>414</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C51" s="24" t="n">
         <f aca="false">(C14-C7)*Inputs_Yearly!$E$17+C7*Inputs_Yearly!$E$21</f>
@@ -47509,7 +47830,7 @@
         <v>415</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C52" s="14" t="n">
         <f aca="false">Inputs!$E$65*C37</f>
@@ -47541,7 +47862,7 @@
         <v>416</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C53" s="24" t="n">
         <f aca="false">C19*C46</f>
@@ -47573,7 +47894,7 @@
         <v>417</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">0+C53</f>
@@ -47601,7 +47922,7 @@
         <v>418</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">0*(1-Inputs!$E$75)/5+C53*(1-Inputs!$E$75)/5*0.5</f>
@@ -47633,7 +47954,7 @@
         <v>419</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C56" s="24" t="n">
         <f aca="false">(C23*Inputs!$E$51+C25+C27)*C47</f>
@@ -47665,7 +47986,7 @@
         <v>420</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C57" s="24" t="n">
         <f aca="false">C40*Inputs!$E$69+(C25+C27)*C34*Inputs!$E$69</f>
@@ -47697,7 +48018,7 @@
         <v>421</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C58" s="24" t="n">
         <f aca="false">0*Inputs!$E$53*Inputs!$E$52*Inputs!$E$70+0*Inputs!$E$55*Inputs!$E$54*Inputs!$E$71</f>
@@ -47729,7 +48050,7 @@
         <v>422</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C59" s="24" t="n">
         <f aca="false">C48+C49+C50+C51+C52+C55+C56+C57+C58</f>
@@ -47761,7 +48082,7 @@
         <v>31</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C60" s="24" t="n">
         <f aca="false">C42-C59</f>
@@ -47833,7 +48154,7 @@
         <v>424</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="14" t="n">
         <f aca="false">Inputs!$E$72*(C6*(Inputs!$E$34*C31+C10*(Inputs!$E$37+Inputs!$E$38)*C31)+C7*(Inputs!$E$36+Inputs!$E$37+Inputs!$E$39)*C31)</f>
@@ -47865,7 +48186,7 @@
         <v>425</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="24" t="n">
         <f aca="false">C5*Inputs!$E$73</f>
@@ -47897,7 +48218,7 @@
         <v>426</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C65" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$57*Inputs!$E$74</f>
@@ -47929,7 +48250,7 @@
         <v>427</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C66" s="24" t="n">
         <f aca="false">C60-C63-C64-C65</f>
@@ -47961,7 +48282,7 @@
         <v>428</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C67" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$61*Inputs_Yearly!$E$65</f>
@@ -47993,7 +48314,7 @@
         <v>429</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C68" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$69+Inputs_Yearly!$E$73+Inputs_Yearly!$E$77+Inputs_Yearly!$E$81+Inputs_Yearly!$E$85+Inputs_Yearly!$E$89+Inputs_Yearly!$E$93+Inputs_Yearly!$E$97+Inputs_Yearly!$E$101+Inputs_Yearly!$E$105+Inputs_Yearly!$E$109+Inputs_Yearly!$E$113</f>
@@ -48025,7 +48346,7 @@
         <v>430</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C69" s="24" t="n">
         <f aca="false">C67+C68</f>
@@ -48057,7 +48378,7 @@
         <v>431</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C70" s="24" t="n">
         <f aca="false">C66-C69</f>
@@ -48089,7 +48410,7 @@
         <v>432</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C71" s="24" t="n">
         <f aca="false">C70+C55-C53</f>
@@ -48121,7 +48442,7 @@
         <v>37</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C72" s="24" t="n">
         <f aca="false">0+C71</f>
@@ -48161,7 +48482,7 @@
         <v>434</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C74" s="24" t="n">
         <f aca="false">C35+C36+C37</f>
@@ -48193,7 +48514,7 @@
         <v>435</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C75" s="24" t="n">
         <f aca="false">C35+C36</f>
@@ -48225,7 +48546,7 @@
         <v>436</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C76" s="24" t="n">
         <f aca="false">C38+C39+C40</f>
@@ -48257,7 +48578,7 @@
         <v>437</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C77" s="24" t="n">
         <f aca="false">C41</f>
@@ -48403,7 +48724,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -48762,7 +49083,7 @@
         <v>381</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$54</f>
@@ -49210,7 +49531,7 @@
         <v>396</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">Inputs!$F$44*Inputs!$F$45+Inputs!$F$46*Inputs!$F$47+Inputs!$F$48*Inputs!$F$49</f>
@@ -49238,7 +49559,7 @@
         <v>397</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="14" t="n">
         <f aca="false">Inputs!$F$46*Inputs!$F$47+Inputs!$F$48*Inputs!$F$49</f>
@@ -49266,7 +49587,7 @@
         <v>398</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">Inputs!$F$44*Inputs!$F$45</f>
@@ -49294,7 +49615,7 @@
         <v>399</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C35" s="24" t="n">
         <f aca="false">(C5+C6)*Inputs!$F$34*C31+C8*Inputs!$F$35+C7*Inputs!$F$36*C31</f>
@@ -49326,7 +49647,7 @@
         <v>400</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C36" s="24" t="n">
         <f aca="false">(C14-C7)*Inputs!$F$38*C31+C7*Inputs!$F$39*C31</f>
@@ -49358,7 +49679,7 @@
         <v>401</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C37" s="24" t="n">
         <f aca="false">C18*Inputs!$F$37*C31+C20*Inputs!$F$37*Inputs!$F$56</f>
@@ -49390,7 +49711,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C38" s="24" t="n">
         <f aca="false">C25*Inputs!$F$40*12</f>
@@ -49422,7 +49743,7 @@
         <v>403</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" s="24" t="n">
         <f aca="false">C23*Inputs!$F$51*Inputs!$F$42+C27*Inputs!$F$57*12</f>
@@ -49454,7 +49775,7 @@
         <v>404</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C40" s="24" t="n">
         <f aca="false">C23*Inputs!$F$50*C32+(C25+C27)*Inputs!$F$50*C33</f>
@@ -49486,7 +49807,7 @@
         <v>405</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C41" s="24" t="n">
         <f aca="false">0*Inputs!$F$53*Inputs!$F$52+0*Inputs!$F$55*Inputs!$F$54</f>
@@ -49518,7 +49839,7 @@
         <v>406</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C42" s="24" t="n">
         <f aca="false">SUM(C35:C41)</f>
@@ -49559,7 +49880,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>33</v>
@@ -49590,7 +49911,7 @@
         <v>408</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C45" s="14" t="n">
         <f aca="false">Inputs!$F$59*(C44+Inputs!$F$60*(1-C44))+Inputs!$F$61*(1-C44)</f>
@@ -49618,7 +49939,7 @@
         <v>409</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C46" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$14</f>
@@ -49646,7 +49967,7 @@
         <v>410</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C47" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$26*Inputs_Yearly!$E$30+Inputs!$F$66*Inputs!$F$67+Inputs!$F$68</f>
@@ -49674,7 +49995,7 @@
         <v>411</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C48" s="24" t="n">
         <f aca="false">(C5+C6)*C45+C8*Inputs!$F$62+C7*Inputs!$F$63</f>
@@ -49706,7 +50027,7 @@
         <v>412</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C49" s="24" t="n">
         <f aca="false">(C5+C6+C8+C7)*Inputs!$F$64</f>
@@ -49738,7 +50059,7 @@
         <v>413</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C50" s="24" t="n">
         <f aca="false">(C18+C20)*C46</f>
@@ -49770,7 +50091,7 @@
         <v>414</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C51" s="24" t="n">
         <f aca="false">(C14-C7)*Inputs_Yearly!$E$18+C7*Inputs_Yearly!$E$22</f>
@@ -49802,7 +50123,7 @@
         <v>415</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C52" s="14" t="n">
         <f aca="false">Inputs!$F$65*C37</f>
@@ -49834,7 +50155,7 @@
         <v>416</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C53" s="24" t="n">
         <f aca="false">C19*C46</f>
@@ -49866,7 +50187,7 @@
         <v>417</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">0+C53</f>
@@ -49894,7 +50215,7 @@
         <v>418</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">0*(1-Inputs!$F$75)/5+C53*(1-Inputs!$F$75)/5*0.5</f>
@@ -49926,7 +50247,7 @@
         <v>419</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C56" s="24" t="n">
         <f aca="false">(C23*Inputs!$F$51+C25+C27)*C47</f>
@@ -49958,7 +50279,7 @@
         <v>420</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C57" s="24" t="n">
         <f aca="false">C40*Inputs!$F$69+(C25+C27)*C34*Inputs!$F$69</f>
@@ -49990,7 +50311,7 @@
         <v>421</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C58" s="24" t="n">
         <f aca="false">0*Inputs!$F$53*Inputs!$F$52*Inputs!$F$70+0*Inputs!$F$55*Inputs!$F$54*Inputs!$F$71</f>
@@ -50022,7 +50343,7 @@
         <v>422</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C59" s="24" t="n">
         <f aca="false">C48+C49+C50+C51+C52+C55+C56+C57+C58</f>
@@ -50054,7 +50375,7 @@
         <v>31</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C60" s="24" t="n">
         <f aca="false">C42-C59</f>
@@ -50126,7 +50447,7 @@
         <v>424</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="14" t="n">
         <f aca="false">Inputs!$F$72*(C6*(Inputs!$F$34*C31+C10*(Inputs!$F$37+Inputs!$F$38)*C31)+C7*(Inputs!$F$36+Inputs!$F$37+Inputs!$F$39)*C31)</f>
@@ -50158,7 +50479,7 @@
         <v>425</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="24" t="n">
         <f aca="false">C5*Inputs!$F$73</f>
@@ -50190,7 +50511,7 @@
         <v>426</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C65" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$58*Inputs!$F$74</f>
@@ -50222,7 +50543,7 @@
         <v>427</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C66" s="24" t="n">
         <f aca="false">C60-C63-C64-C65</f>
@@ -50254,7 +50575,7 @@
         <v>428</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C67" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$62*Inputs_Yearly!$E$66</f>
@@ -50286,7 +50607,7 @@
         <v>429</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C68" s="14" t="n">
         <f aca="false">Inputs_Yearly!$E$70+Inputs_Yearly!$E$74+Inputs_Yearly!$E$78+Inputs_Yearly!$E$82+Inputs_Yearly!$E$86+Inputs_Yearly!$E$90+Inputs_Yearly!$E$94+Inputs_Yearly!$E$98+Inputs_Yearly!$E$102+Inputs_Yearly!$E$106+Inputs_Yearly!$E$110+Inputs_Yearly!$E$114</f>
@@ -50318,7 +50639,7 @@
         <v>430</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C69" s="24" t="n">
         <f aca="false">C67+C68</f>
@@ -50350,7 +50671,7 @@
         <v>431</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C70" s="24" t="n">
         <f aca="false">C66-C69</f>
@@ -50382,7 +50703,7 @@
         <v>432</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C71" s="24" t="n">
         <f aca="false">C70+C55-C53</f>
@@ -50414,7 +50735,7 @@
         <v>37</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C72" s="24" t="n">
         <f aca="false">0+C71</f>
@@ -50454,7 +50775,7 @@
         <v>434</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C74" s="24" t="n">
         <f aca="false">C35+C36+C37</f>
@@ -50486,7 +50807,7 @@
         <v>435</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C75" s="24" t="n">
         <f aca="false">C35+C36</f>
@@ -50518,7 +50839,7 @@
         <v>436</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C76" s="24" t="n">
         <f aca="false">C38+C39+C40</f>
@@ -50550,7 +50871,7 @@
         <v>437</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C77" s="24" t="n">
         <f aca="false">C41</f>
@@ -50968,7 +51289,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -51528,7 +51849,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -51993,52 +52314,42 @@
       </c>
       <c r="D38" s="12"/>
     </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="B39" s="27" t="n">
+        <f aca="false">B34/B35</f>
+        <v>48.562962962963</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>520</v>
+      </c>
+    </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="C40" s="8" t="s">
+      <c r="A40" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="B40" s="27" t="n">
+        <f aca="false">Inputs!$E$77</f>
+        <v>36</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D42" s="8" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="B41" s="17" t="n">
-        <v>950</v>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>600</v>
-      </c>
-      <c r="D41" s="17" t="n">
-        <v>450</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="B42" s="17" t="n">
-        <v>200</v>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>120</v>
-      </c>
-      <c r="D42" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52046,13 +52357,13 @@
         <v>525</v>
       </c>
       <c r="B43" s="17" t="n">
-        <v>180</v>
+        <v>950</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="D43" s="17" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>526</v>
@@ -52063,13 +52374,13 @@
         <v>527</v>
       </c>
       <c r="B44" s="17" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D44" s="17" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>528</v>
@@ -52080,13 +52391,13 @@
         <v>529</v>
       </c>
       <c r="B45" s="17" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D45" s="17" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>530</v>
@@ -52097,13 +52408,13 @@
         <v>531</v>
       </c>
       <c r="B46" s="17" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C46" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D46" s="17" t="n">
         <v>60</v>
-      </c>
-      <c r="D46" s="17" t="n">
-        <v>50</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>532</v>
@@ -52114,62 +52425,96 @@
         <v>533</v>
       </c>
       <c r="B47" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D47" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="C47" s="17" t="n">
+      <c r="E47" s="12" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D48" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="E48" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D49" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="E47" s="12"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="D48" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="E48" s="12"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25" t="s">
-        <v>510</v>
-      </c>
-      <c r="B49" s="30" t="n">
-        <f aca="false">SUM(B41:B48)</f>
-        <v>1680</v>
-      </c>
-      <c r="C49" s="30" t="n">
-        <f aca="false">SUM(C41:C48)</f>
-        <v>1180</v>
-      </c>
-      <c r="D49" s="30" t="n">
-        <f aca="false">SUM(D41:D48)</f>
-        <v>915</v>
-      </c>
+      <c r="E49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="B50" s="24" t="n">
-        <f aca="false">B49-Inputs_Yearly!$E$13</f>
+        <v>538</v>
+      </c>
+      <c r="B50" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C50" s="24" t="n">
-        <f aca="false">C49-Inputs_Yearly!$G$13</f>
+      <c r="C50" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="B51" s="30" t="n">
+        <f aca="false">SUM(B43:B50)</f>
+        <v>1680</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <f aca="false">SUM(C43:C50)</f>
+        <v>1180</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <f aca="false">SUM(D43:D50)</f>
+        <v>915</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="B52" s="24" t="n">
+        <f aca="false">B51-Inputs_Yearly!$E$13</f>
         <v>0</v>
       </c>
-      <c r="D50" s="24" t="n">
-        <f aca="false">D49-Inputs_Yearly!$I$13</f>
+      <c r="C52" s="24" t="n">
+        <f aca="false">C51-Inputs_Yearly!$G$13</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="24" t="n">
+        <f aca="false">D51-Inputs_Yearly!$I$13</f>
         <v>0</v>
       </c>
     </row>

--- a/MH/MH_Robotics_Financial_Model.xlsx
+++ b/MH/MH_Robotics_Financial_Model.xlsx
@@ -983,26 +983,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">대표 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세대 </t>
+      <t xml:space="preserve">대표 세대 </t>
     </r>
     <r>
       <rPr>
@@ -3773,7 +3754,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기본 배치 수용 </t>
+      <t xml:space="preserve">기본 배치 가능 </t>
     </r>
     <r>
       <rPr>
@@ -3792,7 +3773,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">미수용 </t>
+      <t xml:space="preserve">불가 </t>
     </r>
     <r>
       <rPr>
@@ -4552,11 +4533,20 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Time-diary(n=30)</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시간일지 조사 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(n=30)</t>
     </r>
     <r>
       <rPr>
@@ -4638,7 +4628,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인출 </t>
+      <t xml:space="preserve">꺼내기 </t>
     </r>
     <r>
       <rPr>
@@ -5052,7 +5042,35 @@
     <t xml:space="preserve">p_rt_if</t>
   </si>
   <si>
-    <t xml:space="preserve">Interface Kit — Retrofit (Compact Mount · Dock · Vision Reference · Drop Zone)</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interface Kit — Retrofit (Compact Mount · Dock · Vision </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· Drop Zone)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -6663,7 +6681,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Compact Mount · Dock · Vision Reference</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Compact Mount · Dock · Vision </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준점</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">logistics</t>
@@ -6794,7 +6830,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(Failure Rate)</t>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연 고장 횟수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -7400,7 +7455,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">재배치</t>
+      <t xml:space="preserve">후 재임대</t>
     </r>
   </si>
   <si>
@@ -7649,25 +7704,7 @@
     <t xml:space="preserve">new_attach</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신축 입주 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Robot Attach</t>
-    </r>
+    <t xml:space="preserve">신축 입주 시 로봇 구매율</t>
   </si>
   <si>
     <t xml:space="preserve">FUNDING</t>
@@ -9385,7 +9422,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가정 실증 </t>
+      <t xml:space="preserve">실거주 </t>
     </r>
     <r>
       <rPr>
@@ -9404,7 +9441,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">세대 </t>
+      <t xml:space="preserve">세대 실증 </t>
     </r>
     <r>
       <rPr>
@@ -9649,11 +9686,20 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Robot Attach Rate (Remodeling, </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇 동시 구매율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Remodeling, </t>
     </r>
     <r>
       <rPr>
@@ -11050,7 +11096,25 @@
     <t xml:space="preserve">설치 세대 합계</t>
   </si>
   <si>
-    <t xml:space="preserve">Robot Attach Rate (Remodeling)</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇 동시 구매율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Remodeling)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -13406,26 +13470,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">대표 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세대</t>
+      <t xml:space="preserve">대표 세대</t>
     </r>
     <r>
       <rPr>
@@ -16169,7 +16214,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가반 </t>
+      <t xml:space="preserve">가반하중 </t>
     </r>
     <r>
       <rPr>
@@ -16807,7 +16852,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">아파트 재고는 기회 기반이지 구매시장 규모가 아님</t>
+      <t xml:space="preserve">아파트 재고는 잠재 대상이지 실구매 시장 규모가 아님</t>
     </r>
     <r>
       <rPr>
@@ -17364,7 +17409,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Interface + Attach × (Robot + </t>
+      <t xml:space="preserve">Interface + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇 구매율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× (Robot + </t>
     </r>
     <r>
       <rPr>
@@ -18022,17 +18086,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">입주 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Attach × (Robot + </t>
+      <t xml:space="preserve">입주 로봇 구매율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× (Robot + </t>
     </r>
     <r>
       <rPr>
@@ -18502,26 +18566,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구매 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세대 </t>
+      <t xml:space="preserve">구매 세대당 </t>
     </r>
     <r>
       <rPr>
@@ -18827,46 +18872,10 @@
     <t xml:space="preserve">직접판매 획득비용 — 유리</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Failure Rate — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Failure Rate — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유리</t>
-    </r>
+    <t xml:space="preserve">고장 횟수 — 불리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고장 횟수 — 유리</t>
   </si>
   <si>
     <r>
@@ -19373,7 +19382,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Robot Attach Rate 65% ↔ 95%</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로봇 동시 구매율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">65% ↔ 95%</t>
+    </r>
   </si>
   <si>
     <r>
@@ -19411,11 +19438,20 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Failure Rate 1.2 ↔ 0.3</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고장 횟수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.2 ↔ 0.3</t>
     </r>
     <r>
       <rPr>
@@ -19426,6 +19462,25 @@
       </rPr>
       <t xml:space="preserve">회</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년</t>
+    </r>
   </si>
   <si>
     <r>
@@ -19455,7 +19510,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-15pp/+10pp</t>
+      <t xml:space="preserve">-15%p/+10%p</t>
     </r>
   </si>
   <si>
@@ -20728,7 +20783,34 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">· Commissioning </t>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시운전 엔지니어</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">현장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Skill · Data </t>
     </r>
     <r>
       <rPr>
@@ -20741,55 +20823,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">현장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Skill · Data </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">엔지니어</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">S2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현장 서비스 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Technician</t>
-    </r>
+    <t xml:space="preserve">현장 서비스 엔지니어</t>
   </si>
   <si>
     <r>
@@ -21422,7 +21459,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가정 실증 운영 </t>
+      <t xml:space="preserve">실거주 실증 운영 </t>
     </r>
     <r>
       <rPr>
@@ -21579,17 +21616,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예약금 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Test · </t>
+      <t xml:space="preserve">예약금 테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
@@ -25238,26 +25275,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">프리미엄 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kitchen </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동향 </t>
+      <t xml:space="preserve">프리미엄 주방 동향 </t>
     </r>
     <r>
       <rPr>
@@ -26290,7 +26308,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가반 </t>
+      <t xml:space="preserve">가반하중 </t>
     </r>
     <r>
       <rPr>
@@ -27025,7 +27043,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">팔 작업 범위 무릎 높이 이상 </t>
+      <t xml:space="preserve">팔 가동 범위 무릎 높이 이상 </t>
     </r>
     <r>
       <rPr>
@@ -31384,7 +31402,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">식세기 인출 → 수납 → 적재 약 </t>
+      <t xml:space="preserve">식세기 꺼내기 → 수납 → 적재 약 </t>
     </r>
     <r>
       <rPr>
@@ -34592,7 +34610,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>606</v>
       </c>
       <c r="B14" s="11" t="n">
@@ -34649,7 +34667,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>607</v>
       </c>
       <c r="B15" s="11" t="n">
@@ -35353,7 +35371,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="10" t="s">
         <v>627</v>
       </c>
       <c r="B35" s="17" t="n">
@@ -35375,7 +35393,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="10" t="s">
         <v>629</v>
       </c>
       <c r="B37" s="17" t="n">
@@ -37338,7 +37356,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="108.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="119.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>806</v>
       </c>
@@ -39709,7 +39727,7 @@
       <c r="G30" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="10" t="s">
         <v>131</v>
       </c>
     </row>
@@ -42255,7 +42273,7 @@
       <c r="A44" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="10" t="s">
         <v>321</v>
       </c>
       <c r="C44" s="12" t="s">
@@ -42290,7 +42308,7 @@
       <c r="A45" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>321</v>
       </c>
       <c r="C45" s="12" t="s">
@@ -42325,7 +42343,7 @@
       <c r="A46" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="10" t="s">
         <v>321</v>
       </c>
       <c r="C46" s="12" t="s">
@@ -44309,7 +44327,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>375</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -46602,7 +46620,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>375</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -48895,7 +48913,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>375</v>
       </c>
       <c r="B10" s="12" t="s">
